--- a/5/search/FY3_Missile2_results/fine_tuned/comparison.xlsx
+++ b/5/search/FY3_Missile2_results/fine_tuned/comparison.xlsx
@@ -489,19 +489,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>86</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>117.3</v>
+        <v>128</v>
       </c>
       <c r="D3" t="n">
-        <v>27.4</v>
+        <v>24</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6000000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="n">
-        <v>2.900000000000002</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/5/search/FY3_Missile2_results/fine_tuned/comparison.xlsx
+++ b/5/search/FY3_Missile2_results/fine_tuned/comparison.xlsx
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C2" t="n">
-        <v>117.6</v>
+        <v>126</v>
       </c>
       <c r="D2" t="n">
         <v>24</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -489,16 +489,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>88.40000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="C3" t="n">
-        <v>128</v>
+        <v>126.8</v>
       </c>
       <c r="D3" t="n">
         <v>24</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
